--- a/mosip_master/xlsx/loc_hierarchy_list.xlsx
+++ b/mosip_master/xlsx/loc_hierarchy_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chith\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987E270E-8711-441F-A8F3-D7BA84F14BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD064CA-A4E1-41CA-8FE0-71512841EB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$19</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="23">
   <si>
     <t>lang_code</t>
   </si>
@@ -51,139 +51,52 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>دولة</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>Pays</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>المناطق</t>
-  </si>
-  <si>
-    <t>Région</t>
-  </si>
-  <si>
     <t>Province</t>
   </si>
   <si>
-    <t>المحافظة</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>مدينة</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>منطقة</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>رمز بريدي</t>
-  </si>
-  <si>
-    <t>code postal</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>ದೇಶ</t>
-  </si>
-  <si>
-    <t>ಪ್ರದೇಶ</t>
-  </si>
-  <si>
-    <t>ಪ್ರಾಂತ್ಯ</t>
-  </si>
-  <si>
-    <t>ನಗರ</t>
-  </si>
-  <si>
-    <t>ವಲಯ</t>
-  </si>
-  <si>
-    <t>ಕೋಡ್</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>देश</t>
-  </si>
-  <si>
-    <t>क्षेत्रों</t>
-  </si>
-  <si>
-    <t>प्रांत</t>
-  </si>
-  <si>
-    <t>शहर</t>
-  </si>
-  <si>
-    <t>क्षेत्र</t>
-  </si>
-  <si>
-    <t>डाक कोड</t>
-  </si>
-  <si>
     <t>tam</t>
   </si>
   <si>
     <t>நாடு</t>
   </si>
   <si>
-    <t>பிராந்தியம்</t>
-  </si>
-  <si>
     <t>மாகாணம்</t>
   </si>
   <si>
-    <t>நகரம்</t>
-  </si>
-  <si>
-    <t>மண்டலம்</t>
-  </si>
-  <si>
-    <t>குறியீடு</t>
-  </si>
-  <si>
-    <t>spa</t>
-  </si>
-  <si>
-    <t>País</t>
-  </si>
-  <si>
-    <t>Región</t>
-  </si>
-  <si>
-    <t>Provincia</t>
-  </si>
-  <si>
-    <t>Ciudad</t>
-  </si>
-  <si>
-    <t>Zona</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Código Postal</t>
+    <t>sin</t>
+  </si>
+  <si>
+    <t>රට</t>
+  </si>
+  <si>
+    <t>පළාත</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>දිස්ත්‍රික්කය</t>
+  </si>
+  <si>
+    <t>மாவட்டம்</t>
+  </si>
+  <si>
+    <t>Divisional Secretariat Division</t>
+  </si>
+  <si>
+    <t>ප්‍රාදේශීය ලේකම් කොට්ඨාශය</t>
+  </si>
+  <si>
+    <t>பிரதேச செயலகப் பிரிவு</t>
+  </si>
+  <si>
+    <t>Grama Niladhari Division</t>
+  </si>
+  <si>
+    <t>ග්‍රාම නිලධාරී වසම</t>
+  </si>
+  <si>
+    <t>கிராம அலுவலர் பிரிவு</t>
   </si>
 </sst>
 </file>
@@ -566,16 +479,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="25.453125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,7 +502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -603,35 +516,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -639,41 +552,41 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -687,9 +600,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -701,21 +614,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -723,41 +636,41 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -765,417 +678,87 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29">
-        <v>3</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>5</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
-        <v>5</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40">
-        <v>2</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42">
-        <v>4</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="4"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="4"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="4"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C31" s="4"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="4"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="4"/>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
